--- a/Reestructuracion_Expandido.xlsx
+++ b/Reestructuracion_Expandido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\www\Validador2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81D6099-1A6A-4A8F-8C7B-72E2C36BB153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1234FE-0B5C-4AE3-A501-F98C74A8C51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -769,9 +769,6 @@
     <t>Aplicación test de Desarrollo Psicomotor en el rango 24  - 47  meses</t>
   </si>
   <si>
-    <t>&gt;</t>
-  </si>
-  <si>
     <t>Controles de salud realizado por Médico/a, Enfermera/o en el rango 2 meses</t>
   </si>
   <si>
@@ -1142,6 +1139,9 @@
   </si>
   <si>
     <t>SECCION A1: TELEINTERCONSULTA DE ESPECIALIDAD MEDICA POR HOSPITAL DIGITAL</t>
+  </si>
+  <si>
+    <t>&lt;</t>
   </si>
 </sst>
 </file>
@@ -2637,13 +2637,13 @@
         <v>20</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G30" s="9" t="s">
         <v>60</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>236</v>
+        <v>360</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>24</v>
@@ -2652,7 +2652,7 @@
         <v>58</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L30" s="11" t="s">
         <v>59</v>
@@ -2676,13 +2676,13 @@
         <v>20</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>62</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>236</v>
+        <v>360</v>
       </c>
       <c r="I31" s="11" t="s">
         <v>24</v>
@@ -2691,7 +2691,7 @@
         <v>58</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L31" s="11" t="s">
         <v>61</v>
@@ -2715,7 +2715,7 @@
         <v>20</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>144</v>
@@ -2730,7 +2730,7 @@
         <v>63</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L32" s="11" t="s">
         <v>64</v>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="33" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="9" t="s">
@@ -2754,7 +2754,7 @@
         <v>29</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>30</v>
@@ -2769,7 +2769,7 @@
         <v>31</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L33" s="9" t="s">
         <v>32</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="34" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B34" s="9"/>
       <c r="C34" s="9" t="s">
@@ -2793,7 +2793,7 @@
         <v>29</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>33</v>
@@ -2819,7 +2819,7 @@
     </row>
     <row r="35" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9" t="s">
@@ -2832,10 +2832,10 @@
         <v>29</v>
       </c>
       <c r="F35" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="G35" s="11" t="s">
         <v>246</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>247</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>231</v>
@@ -2847,10 +2847,10 @@
         <v>31</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M35" s="9" t="s">
         <v>19</v>
@@ -2871,7 +2871,7 @@
         <v>29</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G36" s="11" t="s">
         <v>36</v>
@@ -2902,7 +2902,7 @@
         <v>29</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G37" s="11" t="s">
         <v>30</v>
@@ -2917,7 +2917,7 @@
         <v>38</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L37" s="9" t="s">
         <v>39</v>
@@ -2941,7 +2941,7 @@
         <v>29</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G38" s="11" t="s">
         <v>40</v>
@@ -2956,7 +2956,7 @@
         <v>38</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L38" s="9" t="s">
         <v>41</v>
@@ -2967,7 +2967,7 @@
     </row>
     <row r="39" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B39" s="9"/>
       <c r="C39" s="9" t="s">
@@ -2980,7 +2980,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G39" s="11" t="s">
         <v>42</v>
@@ -2995,7 +2995,7 @@
         <v>25</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L39" s="11" t="s">
         <v>142</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="40" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B40" s="9"/>
       <c r="C40" s="9" t="s">
@@ -3019,7 +3019,7 @@
         <v>43</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G40" s="11" t="s">
         <v>44</v>
@@ -3034,7 +3034,7 @@
         <v>43</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L40" s="9" t="s">
         <v>45</v>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="41" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="9" t="s">
@@ -3058,7 +3058,7 @@
         <v>46</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G41" s="11" t="s">
         <v>47</v>
@@ -3073,7 +3073,7 @@
         <v>46</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L41" s="9" t="s">
         <v>143</v>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="42" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9" t="s">
@@ -3097,7 +3097,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G42" s="11" t="s">
         <v>48</v>
@@ -3112,7 +3112,7 @@
         <v>49</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L42" s="9" t="s">
         <v>50</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="43" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9" t="s">
@@ -3136,7 +3136,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G43" s="11" t="s">
         <v>51</v>
@@ -3151,7 +3151,7 @@
         <v>49</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L43" s="9" t="s">
         <v>52</v>
@@ -3162,7 +3162,7 @@
     </row>
     <row r="44" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9" t="s">
@@ -3175,7 +3175,7 @@
         <v>25</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>53</v>
@@ -3190,7 +3190,7 @@
         <v>49</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L44" s="9" t="s">
         <v>54</v>
@@ -3214,7 +3214,7 @@
         <v>55</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>56</v>
@@ -3229,7 +3229,7 @@
         <v>57</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L45" s="9" t="s">
         <v>33</v>
@@ -3253,7 +3253,7 @@
         <v>38</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>145</v>
@@ -3268,7 +3268,7 @@
         <v>38</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L46" s="9" t="s">
         <v>146</v>
@@ -3279,7 +3279,7 @@
     </row>
     <row r="47" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9" t="s">
@@ -3292,7 +3292,7 @@
         <v>65</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G47" s="11" t="s">
         <v>66</v>
@@ -3307,7 +3307,7 @@
         <v>65</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L47" s="9" t="s">
         <v>147</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="48" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B48" s="9"/>
       <c r="C48" s="9" t="s">
@@ -3331,7 +3331,7 @@
         <v>67</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G48" s="11" t="s">
         <v>148</v>
@@ -3346,7 +3346,7 @@
         <v>67</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L48" s="9" t="s">
         <v>68</v>
@@ -3357,7 +3357,7 @@
     </row>
     <row r="49" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B49" s="9"/>
       <c r="C49" s="9" t="s">
@@ -3370,7 +3370,7 @@
         <v>70</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G49" s="11" t="s">
         <v>149</v>
@@ -3385,7 +3385,7 @@
         <v>71</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L49" s="9" t="s">
         <v>150</v>
@@ -3396,7 +3396,7 @@
     </row>
     <row r="50" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9" t="s">
@@ -3409,7 +3409,7 @@
         <v>72</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G50" s="11" t="s">
         <v>151</v>
@@ -3424,7 +3424,7 @@
         <v>72</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L50" s="11" t="s">
         <v>152</v>
@@ -3435,7 +3435,7 @@
     </row>
     <row r="51" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B51" s="9"/>
       <c r="C51" s="9" t="s">
@@ -3448,7 +3448,7 @@
         <v>73</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G51" s="11" t="s">
         <v>74</v>
@@ -3463,7 +3463,7 @@
         <v>73</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L51" s="9" t="s">
         <v>75</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="52" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B52" s="9"/>
       <c r="C52" s="9" t="s">
@@ -3487,7 +3487,7 @@
         <v>73</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>76</v>
@@ -3502,7 +3502,7 @@
         <v>73</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L52" s="9" t="s">
         <v>77</v>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="53" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B53" s="9"/>
       <c r="C53" s="9" t="s">
@@ -3526,7 +3526,7 @@
         <v>73</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G53" s="11" t="s">
         <v>78</v>
@@ -3541,7 +3541,7 @@
         <v>73</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L53" s="9" t="s">
         <v>79</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="54" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B54" s="9"/>
       <c r="C54" s="9" t="s">
@@ -3565,7 +3565,7 @@
         <v>73</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G54" s="11" t="s">
         <v>80</v>
@@ -3580,7 +3580,7 @@
         <v>73</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L54" s="9" t="s">
         <v>81</v>
@@ -3604,7 +3604,7 @@
         <v>57</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G55" s="11" t="s">
         <v>153</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="56" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B56" s="9"/>
       <c r="C56" s="9" t="s">
@@ -3635,13 +3635,13 @@
         <v>82</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G56" s="11" t="s">
         <v>83</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>16</v>
@@ -3650,7 +3650,7 @@
         <v>82</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L56" s="11" t="s">
         <v>154</v>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="57" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B57" s="9"/>
       <c r="C57" s="9" t="s">
@@ -3674,7 +3674,7 @@
         <v>84</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G57" s="11" t="s">
         <v>155</v>
@@ -3689,7 +3689,7 @@
         <v>85</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L57" s="9" t="s">
         <v>86</v>
@@ -3700,7 +3700,7 @@
     </row>
     <row r="58" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B58" s="9"/>
       <c r="C58" s="9" t="s">
@@ -3713,7 +3713,7 @@
         <v>87</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G58" s="11" t="s">
         <v>88</v>
@@ -3739,7 +3739,7 @@
     </row>
     <row r="59" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B59" s="9"/>
       <c r="C59" s="9" t="s">
@@ -3752,13 +3752,13 @@
         <v>87</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G59" s="11" t="s">
         <v>90</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I59" s="11" t="s">
         <v>16</v>
@@ -3767,7 +3767,7 @@
         <v>87</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L59" s="9" t="s">
         <v>156</v>
@@ -3788,10 +3788,10 @@
         <v>16</v>
       </c>
       <c r="E60" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="F60" s="11" t="s">
         <v>297</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>298</v>
       </c>
       <c r="G60" s="11" t="s">
         <v>157</v>
@@ -3819,10 +3819,10 @@
         <v>16</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G61" s="11" t="s">
         <v>158</v>
@@ -3850,10 +3850,10 @@
         <v>92</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G62" s="11" t="s">
         <v>159</v>
@@ -3881,10 +3881,10 @@
         <v>92</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G63" s="11" t="s">
         <v>160</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="64" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B64" s="9"/>
       <c r="C64" s="9" t="s">
@@ -3912,10 +3912,10 @@
         <v>92</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G64" s="11" t="s">
         <v>94</v>
@@ -3927,10 +3927,10 @@
         <v>92</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L64" s="9" t="s">
         <v>95</v>
@@ -3941,7 +3941,7 @@
     </row>
     <row r="65" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B65" s="9"/>
       <c r="C65" s="9" t="s">
@@ -3951,10 +3951,10 @@
         <v>92</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G65" s="11" t="s">
         <v>97</v>
@@ -3966,10 +3966,10 @@
         <v>92</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L65" s="9" t="s">
         <v>98</v>
@@ -3980,7 +3980,7 @@
     </row>
     <row r="66" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B66" s="9"/>
       <c r="C66" s="9" t="s">
@@ -3993,7 +3993,7 @@
         <v>99</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>100</v>
@@ -4005,16 +4005,16 @@
         <v>92</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L66" s="9" t="s">
         <v>95</v>
       </c>
       <c r="M66" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4032,7 +4032,7 @@
         <v>99</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G67" s="11" t="s">
         <v>161</v>
@@ -4045,7 +4045,7 @@
       <c r="K67" s="11"/>
       <c r="L67" s="9"/>
       <c r="M67" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4060,10 +4060,10 @@
         <v>92</v>
       </c>
       <c r="E68" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="F68" s="11" t="s">
         <v>313</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>314</v>
       </c>
       <c r="G68" s="11" t="s">
         <v>98</v>
@@ -4076,7 +4076,7 @@
       <c r="K68" s="11"/>
       <c r="L68" s="9"/>
       <c r="M68" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4091,10 +4091,10 @@
         <v>92</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G69" s="11" t="s">
         <v>162</v>
@@ -4122,10 +4122,10 @@
         <v>92</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G70" s="11" t="s">
         <v>163</v>
@@ -4138,7 +4138,7 @@
       <c r="K70" s="11"/>
       <c r="L70" s="9"/>
       <c r="M70" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4153,10 +4153,10 @@
         <v>92</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G71" s="11" t="s">
         <v>164</v>
@@ -4184,10 +4184,10 @@
         <v>92</v>
       </c>
       <c r="E72" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="F72" s="11" t="s">
         <v>321</v>
-      </c>
-      <c r="F72" s="11" t="s">
-        <v>322</v>
       </c>
       <c r="G72" s="11" t="s">
         <v>165</v>
@@ -4218,7 +4218,7 @@
         <v>103</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G73" s="11" t="s">
         <v>166</v>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="74" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B74" s="9"/>
       <c r="C74" s="9" t="s">
@@ -4247,10 +4247,10 @@
         <v>92</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G74" s="11" t="s">
         <v>94</v>
@@ -4262,13 +4262,13 @@
         <v>92</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L74" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M74" s="9" t="s">
         <v>19</v>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="75" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B75" s="9"/>
       <c r="C75" s="9" t="s">
@@ -4286,10 +4286,10 @@
         <v>92</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G75" s="11" t="s">
         <v>124</v>
@@ -4301,13 +4301,13 @@
         <v>92</v>
       </c>
       <c r="J75" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="L75" s="9" t="s">
         <v>324</v>
-      </c>
-      <c r="K75" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>325</v>
       </c>
       <c r="M75" s="9" t="s">
         <v>19</v>
@@ -4325,7 +4325,7 @@
         <v>104</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F76" s="11" t="s">
         <v>105</v>
@@ -4356,7 +4356,7 @@
         <v>104</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>106</v>
@@ -4387,7 +4387,7 @@
         <v>104</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>107</v>
@@ -4418,7 +4418,7 @@
         <v>104</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F79" s="11" t="s">
         <v>105</v>
@@ -4439,7 +4439,7 @@
     </row>
     <row r="80" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B80" s="9"/>
       <c r="C80" s="9" t="s">
@@ -4452,13 +4452,13 @@
         <v>109</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G80" s="11" t="s">
         <v>171</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>108</v>
@@ -4467,7 +4467,7 @@
         <v>109</v>
       </c>
       <c r="K80" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L80" s="11" t="s">
         <v>172</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="81" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B81" s="9"/>
       <c r="C81" s="9" t="s">
@@ -4488,10 +4488,10 @@
         <v>110</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G81" s="11" t="s">
         <v>30</v>
@@ -4517,7 +4517,7 @@
     </row>
     <row r="82" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B82" s="9"/>
       <c r="C82" s="9" t="s">
@@ -4530,10 +4530,10 @@
         <v>114</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H82" s="11" t="s">
         <v>231</v>
@@ -4545,7 +4545,7 @@
         <v>114</v>
       </c>
       <c r="K82" s="11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L82" s="11" t="s">
         <v>115</v>
@@ -4556,7 +4556,7 @@
     </row>
     <row r="83" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B83" s="9"/>
       <c r="C83" s="9" t="s">
@@ -4569,13 +4569,13 @@
         <v>117</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G83" s="11" t="s">
         <v>118</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I83" s="11" t="s">
         <v>116</v>
@@ -4584,7 +4584,7 @@
         <v>119</v>
       </c>
       <c r="K83" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L83" s="9" t="s">
         <v>120</v>
@@ -4595,7 +4595,7 @@
     </row>
     <row r="84" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B84" s="9"/>
       <c r="C84" s="9" t="s">
@@ -4608,13 +4608,13 @@
         <v>117</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G84" s="11" t="s">
         <v>121</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I84" s="11" t="s">
         <v>116</v>
@@ -4623,7 +4623,7 @@
         <v>117</v>
       </c>
       <c r="K84" s="11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L84" s="9" t="s">
         <v>174</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="85" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B85" s="9"/>
       <c r="C85" s="9" t="s">
@@ -4647,7 +4647,7 @@
         <v>123</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G85" s="11" t="s">
         <v>124</v>
@@ -4662,7 +4662,7 @@
         <v>125</v>
       </c>
       <c r="K85" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L85" s="9" t="s">
         <v>126</v>
@@ -4673,7 +4673,7 @@
     </row>
     <row r="86" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B86" s="9"/>
       <c r="C86" s="9" t="s">
@@ -4686,7 +4686,7 @@
         <v>123</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G86" s="11" t="s">
         <v>124</v>
@@ -4701,7 +4701,7 @@
         <v>123</v>
       </c>
       <c r="K86" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="L86" s="9" t="s">
         <v>127</v>
@@ -4712,7 +4712,7 @@
     </row>
     <row r="87" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B87" s="9"/>
       <c r="C87" s="11" t="s">
@@ -4725,7 +4725,7 @@
         <v>123</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G87" s="11" t="s">
         <v>124</v>
@@ -4740,7 +4740,7 @@
         <v>123</v>
       </c>
       <c r="K87" s="11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L87" s="11" t="s">
         <v>128</v>
@@ -4751,7 +4751,7 @@
     </row>
     <row r="88" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B88" s="9"/>
       <c r="C88" s="9" t="s">
@@ -4764,13 +4764,13 @@
         <v>129</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G88" s="11" t="s">
         <v>130</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I88" s="11" t="s">
         <v>122</v>
@@ -4779,7 +4779,7 @@
         <v>129</v>
       </c>
       <c r="K88" s="11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L88" s="9" t="s">
         <v>175</v>
@@ -4790,7 +4790,7 @@
     </row>
     <row r="89" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B89" s="9"/>
       <c r="C89" s="9" t="s">
@@ -4803,13 +4803,13 @@
         <v>131</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G89" s="11" t="s">
         <v>132</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I89" s="11" t="s">
         <v>122</v>
@@ -4818,7 +4818,7 @@
         <v>131</v>
       </c>
       <c r="K89" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L89" s="9" t="s">
         <v>176</v>
@@ -4842,7 +4842,7 @@
         <v>131</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G90" s="11" t="s">
         <v>177</v>
@@ -4874,10 +4874,10 @@
         <v>134</v>
       </c>
       <c r="F91" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="G91" s="11" t="s">
         <v>355</v>
-      </c>
-      <c r="G91" s="11" t="s">
-        <v>356</v>
       </c>
       <c r="H91" s="11" t="s">
         <v>230</v>
@@ -4905,10 +4905,10 @@
         <v>134</v>
       </c>
       <c r="F92" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="G92" s="11" t="s">
         <v>357</v>
-      </c>
-      <c r="G92" s="11" t="s">
-        <v>358</v>
       </c>
       <c r="H92" s="11" t="s">
         <v>230</v>
@@ -4933,13 +4933,13 @@
         <v>135</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F93" s="11" t="s">
         <v>136</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H93" s="11" t="s">
         <v>230</v>

--- a/Reestructuracion_Expandido.xlsx
+++ b/Reestructuracion_Expandido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\www\validador-deis-sso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E067BD-491D-4A97-B74E-26EA6211FC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B39A955-6B03-4A5E-B54E-DD2F1652808D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$M$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$M$130</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="507">
   <si>
     <t>ID</t>
   </si>
@@ -1240,9 +1240,6 @@
     <t>P2</t>
   </si>
   <si>
-    <t>SECCIÓN A</t>
-  </si>
-  <si>
     <t>Población en Control, suma de C12 menos F12 y G12</t>
   </si>
   <si>
@@ -1378,9 +1375,6 @@
     <t>C17</t>
   </si>
   <si>
-    <t>SECCIÓN B</t>
-  </si>
-  <si>
     <t>Metas de Compensación Hba1C&lt; 7%</t>
   </si>
   <si>
@@ -1420,24 +1414,15 @@
     <t>FILA 38</t>
   </si>
   <si>
-    <t>SECCIÓN A1</t>
-  </si>
-  <si>
     <t>Programa Más Adultos Mayores Autovalentes</t>
   </si>
   <si>
     <t>C29+D29</t>
   </si>
   <si>
-    <t>PMAA</t>
-  </si>
-  <si>
     <t>P6</t>
   </si>
   <si>
-    <t>SECCIÓN A.1</t>
-  </si>
-  <si>
     <t>Población en control al corte, personas con diagnóstico de trastorno mentales</t>
   </si>
   <si>
@@ -1453,9 +1438,6 @@
     <t>SUM(C25:C58)</t>
   </si>
   <si>
-    <t>SECCIÓN B.1</t>
-  </si>
-  <si>
     <t>C86</t>
   </si>
   <si>
@@ -1525,9 +1507,6 @@
     <t>SUM(B12:B19)</t>
   </si>
   <si>
-    <t>TODOS EXCEPTO HPU, HRN</t>
-  </si>
-  <si>
     <t xml:space="preserve">SECCION B: GESTANTES EN CONTROL CON EVALUACIÓN RIESGO BIOPSICOSOCIAL </t>
   </si>
   <si>
@@ -1540,15 +1519,6 @@
     <t>SECCION C: GESTANTES EN RIESGO PSICOSOCIAL CON VISITA DOMICILIARIA INTEGRAL REALIZADA EN EL SEMESTRE</t>
   </si>
   <si>
-    <t>SECCIÓN D</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SECCIÓN D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SECCIÓN A </t>
-  </si>
-  <si>
     <t>SECCION D: GESTANTES Y PERSONAS DE 8° MES POST-PARTO EN CONTROL, SEGÚN ESTADO NUTRICIONALL</t>
   </si>
   <si>
@@ -1565,6 +1535,51 @@
   </si>
   <si>
     <t>C12+ (F12-G12)</t>
+  </si>
+  <si>
+    <t>SECCIÓN A: EXISTENCIA DE POBLACIÓN EN CONTROL</t>
+  </si>
+  <si>
+    <t>SECCION D: NIVEL DE CONTROL DE POBLACION RESPIRATORIA CRONICA</t>
+  </si>
+  <si>
+    <t>SECCIÓN A: PROGRAMA SALUD CARDIOVASCULAR (PSCV)</t>
+  </si>
+  <si>
+    <t>SECCIÓN B: METAS DE COMPENSACIÓN</t>
+  </si>
+  <si>
+    <t>SECCION A: POBLACIÓN EN CONTROL POR CONDICIÓN DE FUNCIONALIDAD</t>
+  </si>
+  <si>
+    <t>SECCION A.1: EXISTENCIA DE POBLACIÓN EN CONTROL EN PROGRAMA "MÁS ADULTOS MAYORES AUTOVALENTES" POR CONDICIÓN DE FUNCIONALIDAD</t>
+  </si>
+  <si>
+    <t>SECCION B: POBLACIÓN BAJO CONTROL POR ESTADO NUTRICIONAL</t>
+  </si>
+  <si>
+    <t>SECCION A.1: POBLACIÓN EN CONTROL EN APS AL CORTE</t>
+  </si>
+  <si>
+    <t>SECCION B.1: POBLACIÓN EN CONTROL EN ESPECIALIDAD AL CORTE</t>
+  </si>
+  <si>
+    <t>SECCIÓN A. CLASIFICACIÓN DE LAS FAMILIAS SECTOR URBANO</t>
+  </si>
+  <si>
+    <t>SECCIÓN A.1 CLASIFICACIÓN DE LAS FAMILIAS SECTOR RURAL</t>
+  </si>
+  <si>
+    <t>SECCION A: POBLACIÓN EN CONTROL DEL PROGRAMA DE VIH/SIDA</t>
+  </si>
+  <si>
+    <t>SECCION B: POBLACIÓN EN CONTROL POR COMERCIO SEXUAL</t>
+  </si>
+  <si>
+    <t>SECCIÓN A: PROGRAMA DE CANCER DE CUELLO UTERINO</t>
+  </si>
+  <si>
+    <t>CESFAM</t>
   </si>
 </sst>
 </file>
@@ -1720,21 +1735,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <b/>
@@ -5407,10 +5408,10 @@
         <v>362</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="G94" s="11" t="s">
         <v>363</v>
@@ -5422,7 +5423,7 @@
         <v>362</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="K94" s="11" t="s">
         <v>364</v>
@@ -5448,7 +5449,7 @@
         <v>362</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>366</v>
@@ -5489,7 +5490,7 @@
         <v>362</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="F96" s="11" t="s">
         <v>368</v>
@@ -5504,7 +5505,7 @@
         <v>362</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="K96" s="11" t="s">
         <v>370</v>
@@ -5530,7 +5531,7 @@
         <v>362</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="F97" s="11" t="s">
         <v>371</v>
@@ -5545,7 +5546,7 @@
         <v>362</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="K97" s="11" t="s">
         <v>373</v>
@@ -5571,7 +5572,7 @@
         <v>362</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>375</v>
@@ -5586,7 +5587,7 @@
         <v>362</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="K98" s="11" t="s">
         <v>377</v>
@@ -5612,7 +5613,7 @@
         <v>362</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="F99" s="11" t="s">
         <v>379</v>
@@ -5627,7 +5628,7 @@
         <v>362</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="K99" s="11" t="s">
         <v>381</v>
@@ -5653,7 +5654,7 @@
         <v>362</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>383</v>
@@ -5668,7 +5669,7 @@
         <v>362</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="K100" s="11" t="s">
         <v>385</v>
@@ -5694,7 +5695,7 @@
         <v>362</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="F101" s="11" t="s">
         <v>387</v>
@@ -5709,7 +5710,7 @@
         <v>362</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="K101" s="11" t="s">
         <v>388</v>
@@ -5735,7 +5736,7 @@
         <v>362</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>390</v>
@@ -5776,13 +5777,13 @@
         <v>392</v>
       </c>
       <c r="E103" s="16" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>231</v>
@@ -5791,13 +5792,13 @@
         <v>392</v>
       </c>
       <c r="J103" s="16" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="K103" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="L103" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="L103" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="M103" s="1" t="s">
         <v>19</v>
@@ -5817,10 +5818,10 @@
         <v>392</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>35</v>
@@ -5832,13 +5833,13 @@
         <v>392</v>
       </c>
       <c r="J104" s="16" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="K104" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="L104" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="L104" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="M104" s="1" t="s">
         <v>19</v>
@@ -5858,13 +5859,13 @@
         <v>392</v>
       </c>
       <c r="E105" s="16" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="F105" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="G105" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>401</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>231</v>
@@ -5873,13 +5874,13 @@
         <v>392</v>
       </c>
       <c r="J105" s="16" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="K105" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="L105" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="L105" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="M105" s="1" t="s">
         <v>19</v>
@@ -5899,13 +5900,13 @@
         <v>392</v>
       </c>
       <c r="E106" s="16" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="F106" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="G106" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>231</v>
@@ -5914,13 +5915,13 @@
         <v>392</v>
       </c>
       <c r="J106" s="16" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="K106" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="L106" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="L106" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>19</v>
@@ -5937,37 +5938,37 @@
         <v>14</v>
       </c>
       <c r="D107" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="E107" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="F107" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F107" s="2" t="s">
+      <c r="G107" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>294</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="J107" s="2" t="s">
-        <v>393</v>
+        <v>407</v>
+      </c>
+      <c r="J107" s="16" t="s">
+        <v>492</v>
       </c>
       <c r="K107" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="L107" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="L107" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="M107" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>242</v>
       </c>
@@ -5978,31 +5979,31 @@
         <v>14</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>393</v>
+        <v>407</v>
+      </c>
+      <c r="E108" s="16" t="s">
+        <v>492</v>
       </c>
       <c r="F108" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>294</v>
       </c>
       <c r="I108" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J108" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="K108" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="J108" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="K108" s="2" t="s">
+      <c r="L108" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="L108" s="1" t="s">
-        <v>410</v>
       </c>
       <c r="M108" s="1" t="s">
         <v>19</v>
@@ -6019,31 +6020,31 @@
         <v>14</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>393</v>
+        <v>407</v>
+      </c>
+      <c r="E109" s="16" t="s">
+        <v>492</v>
       </c>
       <c r="F109" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="G109" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>231</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>494</v>
+        <v>407</v>
+      </c>
+      <c r="J109" s="16" t="s">
+        <v>493</v>
       </c>
       <c r="K109" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L109" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="L109" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>19</v>
@@ -6060,31 +6061,31 @@
         <v>14</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>393</v>
+        <v>407</v>
+      </c>
+      <c r="E110" s="16" t="s">
+        <v>492</v>
       </c>
       <c r="F110" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="G110" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>231</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="J110" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J110" s="16" t="s">
         <v>493</v>
       </c>
       <c r="K110" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="L110" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="L110" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="M110" s="1" t="s">
         <v>19</v>
@@ -6101,31 +6102,31 @@
         <v>14</v>
       </c>
       <c r="D111" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E111" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="F111" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F111" s="2" t="s">
+      <c r="G111" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>425</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>294</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>393</v>
+        <v>422</v>
+      </c>
+      <c r="J111" s="16" t="s">
+        <v>494</v>
       </c>
       <c r="K111" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L111" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="L111" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="M111" s="1" t="s">
         <v>19</v>
@@ -6142,37 +6143,37 @@
         <v>14</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>393</v>
+        <v>422</v>
+      </c>
+      <c r="E112" s="16" t="s">
+        <v>494</v>
       </c>
       <c r="F112" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G112" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>429</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>294</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="J112" s="2" t="s">
-        <v>439</v>
+        <v>422</v>
+      </c>
+      <c r="J112" s="16" t="s">
+        <v>495</v>
       </c>
       <c r="K112" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="L112" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="L112" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="M112" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>242</v>
       </c>
@@ -6183,31 +6184,31 @@
         <v>14</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>495</v>
+        <v>422</v>
+      </c>
+      <c r="E113" s="16" t="s">
+        <v>494</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>294</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>439</v>
+        <v>422</v>
+      </c>
+      <c r="J113" s="16" t="s">
+        <v>495</v>
       </c>
       <c r="K113" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="L113" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="L113" s="1" t="s">
-        <v>434</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>19</v>
@@ -6224,31 +6225,31 @@
         <v>14</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>495</v>
+        <v>422</v>
+      </c>
+      <c r="E114" s="16" t="s">
+        <v>494</v>
       </c>
       <c r="F114" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G114" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>294</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>439</v>
+        <v>422</v>
+      </c>
+      <c r="J114" s="16" t="s">
+        <v>495</v>
       </c>
       <c r="K114" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="L114" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="L114" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>19</v>
@@ -6265,28 +6266,28 @@
         <v>14</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>439</v>
+        <v>422</v>
+      </c>
+      <c r="E115" s="16" t="s">
+        <v>495</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>232</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="J115" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="J115" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="K115" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>115</v>
@@ -6295,7 +6296,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>242</v>
       </c>
@@ -6306,37 +6307,37 @@
         <v>14</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>495</v>
+        <v>422</v>
+      </c>
+      <c r="E116" s="16" t="s">
+        <v>494</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>294</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="J116" s="2" t="s">
-        <v>439</v>
+        <v>422</v>
+      </c>
+      <c r="J116" s="16" t="s">
+        <v>495</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="M116" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>242</v>
       </c>
@@ -6347,37 +6348,37 @@
         <v>14</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>495</v>
+        <v>422</v>
+      </c>
+      <c r="E117" s="16" t="s">
+        <v>494</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>294</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="J117" s="2" t="s">
-        <v>439</v>
+        <v>422</v>
+      </c>
+      <c r="J117" s="16" t="s">
+        <v>495</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>242</v>
       </c>
@@ -6388,37 +6389,37 @@
         <v>14</v>
       </c>
       <c r="D118" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E118" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="G118" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>231</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="J118" s="2" t="s">
-        <v>439</v>
+        <v>446</v>
+      </c>
+      <c r="J118" s="16" t="s">
+        <v>498</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="M118" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>188</v>
       </c>
@@ -6429,16 +6430,16 @@
         <v>14</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>453</v>
+        <v>446</v>
+      </c>
+      <c r="E119" s="16" t="s">
+        <v>497</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>230</v>
@@ -6456,7 +6457,7 @@
         <v>361</v>
       </c>
       <c r="M119" s="1" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -6470,13 +6471,13 @@
         <v>14</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
+      </c>
+      <c r="E120" s="16" t="s">
+        <v>499</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>53</v>
@@ -6485,13 +6486,13 @@
         <v>294</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="J120" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
+      </c>
+      <c r="J120" s="16" t="s">
+        <v>499</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="L120" s="1" t="s">
         <v>44</v>
@@ -6500,7 +6501,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>219</v>
       </c>
@@ -6511,13 +6512,13 @@
         <v>14</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
+      </c>
+      <c r="E121" s="16" t="s">
+        <v>499</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>53</v>
@@ -6526,16 +6527,16 @@
         <v>294</v>
       </c>
       <c r="I121" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="J121" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="K121" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="J121" s="2" t="s">
+      <c r="L121" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="K121" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="L121" s="1" t="s">
-        <v>463</v>
       </c>
       <c r="M121" s="1" t="s">
         <v>19</v>
@@ -6552,37 +6553,37 @@
         <v>14</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>464</v>
+        <v>453</v>
+      </c>
+      <c r="E122" s="16" t="s">
+        <v>500</v>
       </c>
       <c r="F122" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="G122" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>294</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="J122" s="2" t="s">
-        <v>464</v>
+        <v>453</v>
+      </c>
+      <c r="J122" s="16" t="s">
+        <v>500</v>
       </c>
       <c r="K122" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="L122" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="L122" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="M122" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>219</v>
       </c>
@@ -6593,31 +6594,31 @@
         <v>14</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>464</v>
+        <v>453</v>
+      </c>
+      <c r="E123" s="16" t="s">
+        <v>500</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>294</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="J123" s="2" t="s">
-        <v>464</v>
+        <v>453</v>
+      </c>
+      <c r="J123" s="16" t="s">
+        <v>500</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="M123" s="1" t="s">
         <v>19</v>
@@ -6634,28 +6635,28 @@
         <v>14</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>393</v>
+        <v>464</v>
+      </c>
+      <c r="E124" s="16" t="s">
+        <v>501</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="J124" s="2" t="s">
-        <v>393</v>
+        <v>464</v>
+      </c>
+      <c r="J124" s="16" t="s">
+        <v>501</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="L124" s="1" t="s">
         <v>30</v>
@@ -6675,31 +6676,31 @@
         <v>14</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>393</v>
+        <v>464</v>
+      </c>
+      <c r="E125" s="16" t="s">
+        <v>501</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="I125" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="J125" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="L125" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="J125" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="L125" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="M125" s="1" t="s">
         <v>19</v>
@@ -6716,31 +6717,31 @@
         <v>14</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>458</v>
+        <v>464</v>
+      </c>
+      <c r="E126" s="16" t="s">
+        <v>502</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="J126" s="2" t="s">
-        <v>458</v>
+        <v>464</v>
+      </c>
+      <c r="J126" s="16" t="s">
+        <v>502</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="M126" s="1" t="s">
         <v>19</v>
@@ -6757,37 +6758,37 @@
         <v>14</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>458</v>
+        <v>464</v>
+      </c>
+      <c r="E127" s="16" t="s">
+        <v>502</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="H127" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="J127" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="L127" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="I127" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="J127" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="K127" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="L127" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="M127" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>188</v>
       </c>
@@ -6798,16 +6799,16 @@
         <v>14</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>393</v>
+        <v>474</v>
+      </c>
+      <c r="E128" s="16" t="s">
+        <v>503</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>230</v>
@@ -6828,7 +6829,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>188</v>
       </c>
@@ -6839,16 +6840,16 @@
         <v>14</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>439</v>
+        <v>474</v>
+      </c>
+      <c r="E129" s="16" t="s">
+        <v>504</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>230</v>
@@ -6869,7 +6870,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>188</v>
       </c>
@@ -6880,16 +6881,16 @@
         <v>14</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>393</v>
+        <v>479</v>
+      </c>
+      <c r="E130" s="16" t="s">
+        <v>505</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>230</v>
@@ -6907,17 +6908,17 @@
         <v>361</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>488</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M93" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M130" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="ERROR">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="ERROR">
       <formula>NOT(ISERROR(SEARCH("ERROR",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="REVISAR">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="REVISAR">
       <formula>NOT(ISERROR(SEARCH("REVISAR",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
